--- a/public/formsExcelTemplates/Admisión - AltaEgreso.xlsx
+++ b/public/formsExcelTemplates/Admisión - AltaEgreso.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Sección</t>
   </si>
@@ -33,25 +33,22 @@
     <t>Institución</t>
   </si>
   <si>
+    <t xml:space="preserve">Clínica Hospital</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nombre del establecimiento</t>
   </si>
   <si>
+    <t xml:space="preserve">San José</t>
+  </si>
+  <si>
     <t xml:space="preserve">Datos del paciente</t>
   </si>
   <si>
-    <t xml:space="preserve">Primer apellido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segundo apellido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primer nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segundo nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipo de documento de identificación</t>
+    <t xml:space="preserve">Nombre completo</t>
+  </si>
+  <si>
+    <t>Cédula</t>
   </si>
   <si>
     <t xml:space="preserve">Estado civil</t>
@@ -64,6 +61,15 @@
   </si>
   <si>
     <t xml:space="preserve">Lugar de nacimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo de sangre</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Contacto</t>
   </si>
   <si>
     <t>Admisiones</t>
@@ -126,7 +132,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="25">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -254,6 +260,15 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -284,31 +299,144 @@
       <diagonal style="none"/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="none"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="none"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="medium">
         <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="medium">
         <color auto="1"/>
       </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color auto="1"/>
       </right>
@@ -318,13 +446,13 @@
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="30">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -342,7 +470,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -351,30 +479,64 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="15" numFmtId="0" xfId="0" applyBorder="1"/>
+    <xf fontId="0" fillId="0" borderId="16" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="17" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="18" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="19" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="20" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="21" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="22" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="10" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="23" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="13" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf fontId="0" fillId="0" borderId="24" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -932,146 +1094,150 @@
       <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6"/>
+      <c r="C2" s="6" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" ht="15">
       <c r="A3" s="7"/>
       <c r="B3" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="9"/>
+        <v>6</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="10"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="13"/>
+      <c r="B4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="12"/>
+    </row>
+    <row r="5" ht="14.4" customHeight="1">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="15"/>
     </row>
     <row r="6">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="13"/>
+      <c r="A6" s="13"/>
+      <c r="B6" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="15"/>
     </row>
     <row r="7">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="13"/>
-    </row>
-    <row r="8" ht="14.4" customHeight="1">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="13"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12" t="s">
+      <c r="A7" s="13"/>
+      <c r="B7" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="13"/>
+      <c r="C7" s="15"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13"/>
+      <c r="B8" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="15"/>
+    </row>
+    <row r="9" ht="15">
+      <c r="A9" s="13"/>
+      <c r="B9" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="18"/>
     </row>
     <row r="10">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="13"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="19"/>
     </row>
     <row r="11">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="13"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="19"/>
     </row>
     <row r="12" ht="15">
-      <c r="A12" s="7"/>
-      <c r="B12" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="14"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="19"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="10"/>
+      <c r="A13" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="23"/>
     </row>
     <row r="14">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="13"/>
-    </row>
-    <row r="15" ht="15">
-      <c r="A15" s="7"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="15"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="24"/>
       <c r="B15" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="14"/>
+        <v>21</v>
+      </c>
+      <c r="C15" s="25"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="s">
-        <v>20</v>
+      <c r="A16" s="26" t="s">
+        <v>22</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="10"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="13"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="13"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12" t="s">
+      <c r="C16" s="12"/>
+    </row>
+    <row r="17" ht="15">
+      <c r="A17" s="21"/>
+      <c r="B17" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="13"/>
-    </row>
-    <row r="20" ht="15">
-      <c r="A20" s="7"/>
+      <c r="C17" s="15"/>
+    </row>
+    <row r="18" ht="14.25">
+      <c r="A18" s="21"/>
+      <c r="B18" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="15"/>
+    </row>
+    <row r="19" ht="14.25">
+      <c r="A19" s="21"/>
+      <c r="B19" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="15"/>
+    </row>
+    <row r="20" ht="14.25">
+      <c r="A20" s="24"/>
       <c r="B20" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="14"/>
+        <v>27</v>
+      </c>
+      <c r="C20" s="25"/>
     </row>
     <row r="21" ht="14.25">
-      <c r="A21" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="17"/>
+      <c r="A21" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="5">
